--- a/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/菲律宾部署方案-v2.3-修订版.xlsx
@@ -2300,7 +2300,7 @@
       </c>
       <c r="K10" s="34" t="inlineStr">
         <is>
-          <t>国际站默认配额常不足；工单需说明业务场景与峰值，分两批（先马尼拉后新加坡）申请。新加坡 ≥64 vCPU 的依据是「单站点全量接管 = 被接管站点 maxReplicas 16 × 1.5 = 24 副本」：24 × Pod request 2 vCPU = 48 vCPU，÷ 7.9 vCPU/节点 ≈ 7 节点，留 ≥20% 给 kube-system → 8 节点 = 64 vCPU。【分期口径】本期新加坡仅承载 PH 备、不含泰国备，因此不按「PH 备 + TH 备 同时接管」的 96 vCPU（≥13 节点）申请；二期引入 TH 备时须重新提工单</t>
+          <t>国际站默认配额常不足；工单需说明业务场景与峰值，分两批（先马尼拉后新加坡）申请。新加坡 ≥64 vCPU 的依据是「单站点全量接管 = 被接管站点 maxReplicas 16 × 1.5 = 24 副本」：24 × Pod request 2 vCPU = 48 vCPU，÷ 7.9 vCPU/节点 ≈ 7 节点，留 ≥20% 给 kube-system → 8 节点 = 64 vCPU。【分期口径】本期新加坡仅承载 PH 备、不含泰国备，因此不按「PH 备 + TH 备 同时接管」的 96 vCPU（含 ≥20% 系统组件余量即 ≥16 节点 / 128 vCPU）申请；二期引入 TH 备时须重新提工单</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
         <is>
           <t>重申红线：
 新加坡【不部署 RDS PostgreSQL】（含只读副本与 DTS）。备 region 仅通过公网 TLS（verify-full + IP 白名单）读写马尼拉主库，仅故障接管时生效，不做双写。staging / perf 环境位于马尼拉主站点（主站 RDS 的逻辑隔离 schema），不构成对本红线的例外。
-【容量要求】备 region 可扩容上限 = 被接管站点 maxReplicas 16 × 1.5 = 24 副本（常备 2 副本 + HPA 2–24 + 节点池自动伸缩 2–8，即 8 × 8 = 64 vCPU）。【分期口径】本期新加坡仅承载 PH 备、不含泰国备；二期引入 TH 备时须重算节点池上限（两地同时接管需 48 副本 / ≥13 节点）并重新申请配额。</t>
+【容量要求】备 region 可扩容上限 = 被接管站点 maxReplicas 16 × 1.5 = 24 副本（常备 2 副本 + HPA 2–24 + 节点池自动伸缩 2–8，即 8 × 8 = 64 vCPU）。【分期口径】本期新加坡仅承载 PH 备、不含泰国备；二期引入 TH 备时须重算节点池上限（两地同时接管需 48 副本 / 96 vCPU，含 ≥20% 余量即 ≥16 节点 / 128 vCPU）并重新申请配额。</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
@@ -15755,9 +15755,9 @@
   <mergeCells count="12">
     <mergeCell ref="A61:AD61"/>
     <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A83:AD83"/>
+    <mergeCell ref="J2:L2"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="B65:AD65"/>
     <mergeCell ref="A1:X1"/>

--- a/菲律宾部署方案-v2.3-修订版.xlsx
+++ b/菲律宾部署方案-v2.3-修订版.xlsx
@@ -1413,7 +1413,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>v2.2（工期压缩版；v2.0 -&gt; v2.1 -&gt; v2.2 修订依据见「修订要点」）</t>
+          <t>v2.3（容量口径修订 + 三项遗留决策定案；v2.0 -&gt; v2.1 -&gt; v2.2 -&gt; v2.3 修订依据见「修订要点」）</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>高：5 天口径利用率 94.2%，仅余 7 人时缓冲（约 1.75 段/人），且为连续 5 天 × 12 小时（含晚间加班段）作业；任一人阻塞/请假、任一外部依赖（配额审批、实名认证、代码侧改造交付）延期即直接顺延，无内部消化空间。缓解措施与可选替代方案见「里程碑与验收」风险表、裁剪预案与工期口径变更说明</t>
+          <t>高：5 天口径利用率 94.2%，仅余 7 人时缓冲（约 1.75 段/人），且为连续 5 天 × 12 小时（含晚间加班段）作业；任一人阻塞/请假、任一外部依赖（配额审批、实名认证、代码侧改造交付）延期即直接顺延，无内部消化空间。缓解措施与可选替代方案见「里程碑与验收」风险表、裁剪预案与工期口径变更说明。三项遗留决策已于 2026-09-24 定案：① 保留 D4/D5 国庆窗口，不采用顺延至 2026-10-08 的方案，改为锁定假期值班与工单加急；② T-5 = 2026-09-23 已过，本次不改基准、不顺延 D1；③ 本期不增加第 3 人，人力冗余风险由 A/B 互备与裁剪预案收敛。三项均为风险自担项，处置与残余风险见「里程碑与验收」风险表 A13 / A16 / A28 行。</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
     <row r="18" ht="57" customHeight="1" s="11">
       <c r="A18" s="41" t="inlineStr">
         <is>
-          <t>修订要点（v2.0 -&gt; v2.1）</t>
+          <t>修订要点（v2.0 -&gt; v2.3）</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；瓶颈是 2 人的绝对产能（113 人时 / 120 人时 = 94.2%）而非依赖串行（关键路径仅 9 段），因此「延长每段时间」的加班方式无解（2 段/天即使单人 7 人时/段亦逼近上限），必须改为「增加一个工作段」</t>
+          <t>① 工期 5 天 -&gt; 9 天（v2.0 -&gt; v2.1：56 项任务压缩进 8 天/16 时段经 600 次重排无可行解）；② 前置期 T-3 的 0 天改为真实前置 T-5；③ 补 PgBouncer/RDS 代理、cluster-autoscaler、备 region HPA 与 1.5× 接管容量；④ 补 staging/perf、运维访问面、Tair 预热、PITR 演练、连接数预算、Grafana、带宽与成本量化、上游配额盘点；⑤ 安全 3 改（ALB 源收敛为 WAF/DCDN 回源段、支付回调源 IP 白名单、SESSION_SECRET 双密钥轮换）；⑥ 修正证书部署时序、依赖倒挂、J48 负荷公式、门禁计数与编号映射、域名/数据盘/RTT 阈值口径；⑦【v2.2】工期 9 天 -&gt; 5 天：把每天 2 个半天时段改为 3 个工作段（新增 19:00–23:00 晚间加班段），15 时段 × 2 人 × 4 人时 = 120 人时产能，56 项任务在 15 段内重排完成、0 超载；瓶颈是 2 人的绝对产能（113 人时 / 120 人时 = 94.2%）而非依赖串行（关键路径仅 9 段），因此「延长每段时间」的加班方式无解（2 段/天即使单人 7 人时/段亦逼近上限），必须改为「增加一个工作段」；⑧【v2.3】备 region 容量口径改为「本期仅承载 PH 备、不含泰国备」：节点数按 Pod requests 反算并留 ≥ 20% 系统组件余量 → 8 节点，节点池 2–12 改 2–8、配额 96 改 64 vCPU（与马尼拉主站同额）；统一「1.5×」基准为 maxReplicas 16 × 1.5 = 24 副本；修正「资源清单-新加坡」与「后续泰国备可复用本集群」跟「泰国备为二期、不共用本集群」的口径矛盾；⑨【2026-09-24 决策定案】三项遗留决策：保留 D4/D5 国庆窗口（不顺延）、T-5 = 2026-09-23 基准不动、本期不增加第 3 人；处置与残余风险见「里程碑与验收」风险表 A13 / A16 / A28 行</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>2 人全职 —— 人员A：基础设施/网络/接入/SRE；人员B：数据/应用/CI-CD/DevOps</t>
+          <t>2 人全职 —— 人员A：基础设施/网络/接入/SRE；人员B：数据/应用/CI-CD/DevOps（已决策 2026-09-24：本期不增加第 3 人）</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>每时段 = 4 小时，单人每时段上限 4 人时；每天 3 个时段 = 2 人 × 12 小时 = 24 人时/天；5 天共 15 个时段（S1–S15）= 120 人时产能。（对比：v2.1 的 9 天口径为 2 人 × 8 小时/天 × 9 天 = 144 人时）</t>
+          <t>每时段 = 4 小时，单人每时段上限 4 人时；每天 3 个时段 = 2 人 × 12 小时 = 24 人时/天；5 天共 15 个时段（S1–S15）= 120 人时产能。（对比：v2.1 的 9 天口径为 2 人 × 8 小时/天 × 9 天 = 144 人时）。已决策（2026-09-24）：本期维持 2 人、不增加第 3 人，7 人时缓冲（94.2% 利用率）为可接受的剩余风险。</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
     <row r="32">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>日期口径：D1 = 部署启动日（2026-09-28），落地计划中每项任务的日期均由此基准自动推算；任务均为「工作段」粒度，D1 上午 = S1、D1 下午 = S2、D1 晚间 = S3 …… D5 晚间 = S15；每天 3 段 = 上午 09:00–13:00 / 下午 14:00–18:00 / 晚间 19:00–23:00（晚间为加班段，建议仅排低风险任务，关键变更与上线操作集中在 S1/S2）。数据来源：资源规格、数量与关键配置取自 impl_deploy.md 第 7.2 / 7.4 / 7.9 / 8.5 节；人时与配额为估算口径，需按实际情况与团队熟练度校准。</t>
+          <t>日期口径：D1 = 部署启动日（2026-09-28），落地计划中每项任务的日期均由此基准自动推算；任务均为「工作段」粒度，D1 上午 = S1、D1 下午 = S2、D1 晚间 = S3 …… D5 晚间 = S15；每天 3 段 = 上午 09:00–13:00 / 下午 14:00–18:00 / 晚间 19:00–23:00（晚间为加班段，建议仅排低风险任务，关键变更与上线操作集中在 S1/S2）。数据来源：资源规格、数量与关键配置取自 impl_deploy.md 第 7.2 / 7.4 / 7.9 / 8.5 节；人时与配额为估算口径，需按实际情况与团队熟练度校准。前置期口径：T-5 = 2026-09-23（编制日 2026-09-24 时该时点已过）；经 2026-09-24 决策保持原基准不变、不顺延 D1，前置项（G1–G13）若未在本基准内闭环，仍按门禁规则顺延 D1（见风险表 A13 行）。</t>
         </is>
       </c>
       <c r="B32" s="9" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>未通过则 5 天工期不可达，必须顺延（D1 不得启动）</t>
+          <t>未通过则 5 天工期不可达，必须顺延（D1 不得启动）。决策留痕（2026-09-24）：前置启动日 T-5 = 2026-09-23 编制时已过，本次维持原基准不变、不顺延 D1；G1–G13 未在本基准内闭环时，仍按本节门禁规则顺延。</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>唯一的外部不可控项，已在 G1/G2 列为门禁</t>
+          <t>唯一的外部不可控项，已在 G1/G2 列为门禁。决策留痕（2026-09-24）：T-5 = 2026-09-23 已过，本期不改基准、不顺延 D1，接受该项剩余风险；T-5 后每日 18:00 跟进而未批复的，D1 即顺延（顺延不改变工期仍为 5 天的结论）。</t>
         </is>
       </c>
     </row>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>明确 A/B 分工并互备关键命令；每日 3 次短站会（每段结束 10 分钟）同步阻碍项；关键变更与上线操作集中在 S1/S2，晚间加班段只排低风险任务。本版缓冲仅 7 人时（约 1.75 段/人），无法覆盖任一人单日缺席 —— 需预留第 3 人作为应急替补</t>
+          <t>明确 A/B 分工并互备关键命令；每日 3 次短站会（每段结束 10 分钟）同步阻碍项；关键变更与上线操作集中在 S1/S2，晚间加班段只排低风险任务。已决策（2026-09-24）：本期不增加第 3 人。本版缓冲仅 7 人时（约 1.75 段/人），无法覆盖任一人单日缺席，人力冗余风险改由以下方式收敛：① A/B 关键命令互备，每段结束 10 分钟交接并留书面记录；② 单日任务完成率 &lt; 80% 即触发「工期裁剪预案」，自第 1 项（DCDN 延后）起顺序降级；③ 任一人员缺席当天即停止关键变更，只执行可回退任务并按 G0 规则顺延。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -16291,12 +16291,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>需临时补充第三人</t>
+          <t>接受（本期不加第 3 人）；触发时按工期裁剪预案降级交付范围兜底</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>A 负责网络/接入，B 负责数据/应用；5 天口径下缓冲由 31 人时降至 7 人时</t>
+          <t>A 负责网络/接入，B 负责数据/应用；5 天口径下缓冲由 31 人时降至 7 人时。决策留痕（2026-09-24）：不增加第 3 人，7 人时缓冲的剩余风险由裁剪预案与 A/B 互备兜底。</t>
         </is>
       </c>
     </row>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>① T-3 前确认假期值班排班与工单加急通道并留存回执；② 或整体顺延 D1 至 2026-10-08（节后首个工作日起），工期仍为 5 天，总交付不晚于 2026-10-14；③ 或把 M4/M5 的里程碑签署改为节后补签，部署动作本身不停</t>
+          <t>已决策（2026-09-24）：保留 D4/D5 窗口、不顺延（否决原 ② 顺延至 2026-10-08 的方案）。执行原 ①：T-3 前确认假期值班排班与工单加急通道并留存回执；原 ③（M4/M5 签署改为节后补签、部署动作本身不停）作为兜底。风险自担：假期内的工单响应、上游白名单回执与验收签字延迟，不再作为 D 序列顺延的理由。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>顺延 3–9 天</t>
+          <t>顺延 0–3 天（窗口保留为已决策，不因假期额外顺延；超出部分由裁剪预案吸收）</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>仅影响中国境内团队；若实施方为境外或菲律宾本地团队，或已按 ② 顺延，则本项不成立</t>
+          <t>仅影响中国境内团队；若实施方为境外或菲律宾本地团队则本项不成立。决策留痕（2026-09-24）：保留 D4/D5 窗口、不顺延，已否决 ② 方案（原 ②：D1 顺延至 2026-10-08、总交付不晚于 2026-10-14，仅作追溯保留）。</t>
         </is>
       </c>
     </row>
